--- a/ig/DM-OCTOBRE-2025/ValueSet-JDV-J198-FonctionLieu-ROR.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-JDV-J198-FonctionLieu-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250620120000</t>
+    <t>20251017120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-20T12:00:00+01:00</t>
+    <t>2025-10-17T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -175,6 +175,12 @@
   </si>
   <si>
     <t>Salle de travail (salle de naissance)</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>Bloc obstétrical</t>
   </si>
   <si>
     <t/>
@@ -445,7 +451,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -569,15 +575,23 @@
         <v>54</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
